--- a/Toeic/part1/スキマ時間で毎日TOEIC学習【TOEICリスニング対策/ReviewWords.xlsx
+++ b/Toeic/part1/スキマ時間で毎日TOEIC学習【TOEICリスニング対策/ReviewWords.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EnglishLearnning3\Toeic\part1\スキマ時間で毎日TOEIC学習【TOEICリスニング対策\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51F63FC1-50B8-49BA-96BF-EB730E3FFB4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F38F5A4A-A0A7-4FB1-BD21-4D276FBC1EFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="29" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="60">
   <si>
     <t>word</t>
     <phoneticPr fontId="1"/>
@@ -76,13 +76,168 @@
   <si>
     <t>意思</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>parasols</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>日傘</t>
+  </si>
+  <si>
+    <t>体を丸める</t>
+  </si>
+  <si>
+    <t>curled up</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>trotting across</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コトコと駆け足で横切っています</t>
+  </si>
+  <si>
+    <t>小跑着穿过</t>
+  </si>
+  <si>
+    <t>medow</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>牧草地</t>
+  </si>
+  <si>
+    <t>astride</t>
+  </si>
+  <si>
+    <t>跨って</t>
+  </si>
+  <si>
+    <t>grazing</t>
+  </si>
+  <si>
+    <t>草を食む</t>
+  </si>
+  <si>
+    <t>tram</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>路面電車</t>
+  </si>
+  <si>
+    <t>有轨电车</t>
+  </si>
+  <si>
+    <t>overtaking</t>
+  </si>
+  <si>
+    <t>追い越し</t>
+  </si>
+  <si>
+    <t>Drawn shut</t>
+  </si>
+  <si>
+    <t>閉められた</t>
+  </si>
+  <si>
+    <t>gazing</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>じっと見つめる</t>
+  </si>
+  <si>
+    <t>campfire</t>
+  </si>
+  <si>
+    <t>キャンプファイヤー</t>
+  </si>
+  <si>
+    <t>营火</t>
+  </si>
+  <si>
+    <t>crouching</t>
+  </si>
+  <si>
+    <t>しゃがむ</t>
+  </si>
+  <si>
+    <t>蹲伏</t>
+  </si>
+  <si>
+    <t>屋台</t>
+  </si>
+  <si>
+    <t>stalls</t>
+  </si>
+  <si>
+    <t>reins</t>
+  </si>
+  <si>
+    <t>手綱</t>
+  </si>
+  <si>
+    <t>horse-drawn</t>
+  </si>
+  <si>
+    <t>馬車の</t>
+  </si>
+  <si>
+    <t>docked</t>
+  </si>
+  <si>
+    <t>停泊</t>
+  </si>
+  <si>
+    <t>strolling</t>
+  </si>
+  <si>
+    <t>ぶらぶら歩く</t>
+  </si>
+  <si>
+    <t>Stable</t>
+  </si>
+  <si>
+    <t>きゅうしゃ</t>
+  </si>
+  <si>
+    <t>roaming</t>
+  </si>
+  <si>
+    <t>漫游</t>
+  </si>
+  <si>
+    <t>ぶらぶらと</t>
+  </si>
+  <si>
+    <t>pavement</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>歩道</t>
+    <rPh sb="0" eb="2">
+      <t>ホドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>tactile paving strip</t>
+  </si>
+  <si>
+    <t>視覚障害者誘導用ブロック</t>
+  </si>
+  <si>
+    <t>触觉铺装块</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -111,6 +266,18 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF444444"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -132,7 +299,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -144,6 +311,8 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -424,10 +593,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9737CE88-328B-4BF9-A55E-800C789209EE}">
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:L49"/>
   <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="5" max="5" width="31.69921875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:12">
       <c r="A1" s="4"/>
       <c r="B1" s="3" t="s">
         <v>1</v>
@@ -445,7 +617,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:12">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -455,7 +627,7 @@
       <c r="C2" s="2"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:12">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -465,7 +637,7 @@
       <c r="C3" s="2"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:12">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -473,9 +645,14 @@
         <v>2</v>
       </c>
       <c r="C4" s="2"/>
-      <c r="D4" s="1"/>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="D4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -483,9 +660,14 @@
         <v>4</v>
       </c>
       <c r="C5" s="2"/>
-      <c r="D5" s="1"/>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="D5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="36">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -493,9 +675,35 @@
         <v>2</v>
       </c>
       <c r="C6" s="2"/>
-      <c r="D6" s="1"/>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="D6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -505,7 +713,7 @@
       <c r="C7" s="2"/>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:12">
       <c r="A8" s="4">
         <v>1</v>
       </c>
@@ -513,9 +721,17 @@
         <v>4</v>
       </c>
       <c r="C8" s="2"/>
-      <c r="D8" s="1"/>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="D8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
       <c r="A9" s="4">
         <v>2</v>
       </c>
@@ -523,9 +739,14 @@
         <v>4</v>
       </c>
       <c r="C9" s="2"/>
-      <c r="D9" s="1"/>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="D9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10" s="4">
         <v>3</v>
       </c>
@@ -533,9 +754,20 @@
         <v>2</v>
       </c>
       <c r="C10" s="2"/>
-      <c r="D10" s="1"/>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="D10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
       <c r="A11" s="4">
         <v>4</v>
       </c>
@@ -543,9 +775,17 @@
         <v>4</v>
       </c>
       <c r="C11" s="2"/>
-      <c r="D11" s="1"/>
-    </row>
-    <row r="12" spans="1:6">
+      <c r="D11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12" s="4">
         <v>5</v>
       </c>
@@ -553,9 +793,17 @@
         <v>2</v>
       </c>
       <c r="C12" s="2"/>
-      <c r="D12" s="1"/>
-    </row>
-    <row r="13" spans="1:6">
+      <c r="D12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
       <c r="A13" s="4">
         <v>6</v>
       </c>
@@ -563,9 +811,26 @@
         <v>2</v>
       </c>
       <c r="C13" s="2"/>
-      <c r="D13" s="1"/>
-    </row>
-    <row r="14" spans="1:6">
+      <c r="D13" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13" t="s">
+        <v>42</v>
+      </c>
+      <c r="G13" t="s">
+        <v>43</v>
+      </c>
+      <c r="H13" t="s">
+        <v>44</v>
+      </c>
+      <c r="I13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
       <c r="A14" s="4">
         <v>1</v>
       </c>
@@ -573,9 +838,14 @@
         <v>2</v>
       </c>
       <c r="C14" s="2"/>
-      <c r="D14" s="1"/>
-    </row>
-    <row r="15" spans="1:6">
+      <c r="D14" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
       <c r="A15" s="4">
         <v>2</v>
       </c>
@@ -583,9 +853,14 @@
         <v>4</v>
       </c>
       <c r="C15" s="2"/>
-      <c r="D15" s="1"/>
-    </row>
-    <row r="16" spans="1:6">
+      <c r="D15" t="s">
+        <v>48</v>
+      </c>
+      <c r="E15" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
       <c r="A16" s="4">
         <v>3</v>
       </c>
@@ -593,9 +868,14 @@
         <v>4</v>
       </c>
       <c r="C16" s="2"/>
-      <c r="D16" s="1"/>
-    </row>
-    <row r="17" spans="1:4">
+      <c r="D16" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" s="4">
         <v>4</v>
       </c>
@@ -603,9 +883,17 @@
         <v>4</v>
       </c>
       <c r="C17" s="2"/>
-      <c r="D17" s="1"/>
-    </row>
-    <row r="18" spans="1:4">
+      <c r="D17" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E17" t="s">
+        <v>54</v>
+      </c>
+      <c r="F17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" s="4">
         <v>5</v>
       </c>
@@ -613,9 +901,14 @@
         <v>4</v>
       </c>
       <c r="C18" s="2"/>
-      <c r="D18" s="1"/>
-    </row>
-    <row r="19" spans="1:4">
+      <c r="D18" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" s="4">
         <v>6</v>
       </c>
@@ -623,9 +916,17 @@
         <v>4</v>
       </c>
       <c r="C19" s="2"/>
-      <c r="D19" s="1"/>
-    </row>
-    <row r="20" spans="1:4">
+      <c r="D19" t="s">
+        <v>57</v>
+      </c>
+      <c r="E19" t="s">
+        <v>58</v>
+      </c>
+      <c r="F19" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" s="4">
         <v>1</v>
       </c>
@@ -633,7 +934,7 @@
       <c r="C20" s="2"/>
       <c r="D20" s="1"/>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:6">
       <c r="A21" s="4">
         <v>2</v>
       </c>
@@ -641,7 +942,7 @@
       <c r="C21" s="2"/>
       <c r="D21" s="1"/>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:6">
       <c r="A22" s="4">
         <v>3</v>
       </c>
@@ -649,7 +950,7 @@
       <c r="C22" s="2"/>
       <c r="D22" s="1"/>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:6">
       <c r="A23" s="4">
         <v>4</v>
       </c>
@@ -657,7 +958,7 @@
       <c r="C23" s="2"/>
       <c r="D23" s="1"/>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:6">
       <c r="A24" s="4">
         <v>5</v>
       </c>
@@ -665,7 +966,7 @@
       <c r="C24" s="2"/>
       <c r="D24" s="1"/>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:6">
       <c r="A25" s="4">
         <v>6</v>
       </c>
@@ -673,7 +974,7 @@
       <c r="C25" s="2"/>
       <c r="D25" s="1"/>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:6">
       <c r="A26" s="4">
         <v>1</v>
       </c>
@@ -681,7 +982,7 @@
       <c r="C26" s="2"/>
       <c r="D26" s="1"/>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:6">
       <c r="A27" s="4">
         <v>2</v>
       </c>
@@ -689,7 +990,7 @@
       <c r="C27" s="2"/>
       <c r="D27" s="1"/>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:6">
       <c r="A28" s="4">
         <v>3</v>
       </c>
@@ -697,7 +998,7 @@
       <c r="C28" s="2"/>
       <c r="D28" s="1"/>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:6">
       <c r="A29" s="4">
         <v>4</v>
       </c>
@@ -705,7 +1006,7 @@
       <c r="C29" s="2"/>
       <c r="D29" s="1"/>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:6">
       <c r="A30" s="4">
         <v>5</v>
       </c>
@@ -713,7 +1014,7 @@
       <c r="C30" s="2"/>
       <c r="D30" s="1"/>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:6">
       <c r="A31" s="4">
         <v>6</v>
       </c>
@@ -721,7 +1022,7 @@
       <c r="C31" s="2"/>
       <c r="D31" s="1"/>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:6">
       <c r="A32" s="4">
         <v>1</v>
       </c>

--- a/Toeic/part1/スキマ時間で毎日TOEIC学習【TOEICリスニング対策/ReviewWords.xlsx
+++ b/Toeic/part1/スキマ時間で毎日TOEIC学習【TOEICリスニング対策/ReviewWords.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EnglishLearnning3\Toeic\part1\スキマ時間で毎日TOEIC学習【TOEICリスニング対策\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F38F5A4A-A0A7-4FB1-BD21-4D276FBC1EFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFBD8586-2941-45E5-8F46-23641B19178A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="29" r:id="rId1"/>
-    <sheet name="template" sheetId="20" r:id="rId2"/>
-    <sheet name="list" sheetId="2" state="hidden" r:id="rId3"/>
+    <sheet name="2" sheetId="30" r:id="rId2"/>
+    <sheet name="template" sheetId="20" r:id="rId3"/>
+    <sheet name="list" sheetId="2" state="hidden" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="64">
   <si>
     <t>word</t>
     <phoneticPr fontId="1"/>
@@ -231,6 +232,18 @@
   </si>
   <si>
     <t>触觉铺装块</t>
+  </si>
+  <si>
+    <t>Gripping</t>
+  </si>
+  <si>
+    <t>握りしめている</t>
+  </si>
+  <si>
+    <t>trekking poles</t>
+  </si>
+  <si>
+    <t>トレッキングポール</t>
   </si>
 </sst>
 </file>
@@ -596,7 +609,10 @@
   <dimension ref="A1:L49"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
+    <col min="4" max="4" width="19.19921875" customWidth="1"/>
     <col min="5" max="5" width="31.69921875" customWidth="1"/>
+    <col min="8" max="8" width="14.59765625" customWidth="1"/>
+    <col min="9" max="9" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -644,7 +660,9 @@
       <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="2"/>
+      <c r="C4" s="2" t="s">
+        <v>4</v>
+      </c>
       <c r="D4" s="1" t="s">
         <v>12</v>
       </c>
@@ -674,7 +692,9 @@
       <c r="B6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="2"/>
+      <c r="C6" s="2" t="s">
+        <v>4</v>
+      </c>
       <c r="D6" s="1" t="s">
         <v>16</v>
       </c>
@@ -753,7 +773,9 @@
       <c r="B10" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="2"/>
+      <c r="C10" s="2" t="s">
+        <v>4</v>
+      </c>
       <c r="D10" t="s">
         <v>30</v>
       </c>
@@ -784,6 +806,18 @@
       <c r="F11" t="s">
         <v>36</v>
       </c>
+      <c r="G11" t="s">
+        <v>60</v>
+      </c>
+      <c r="H11" t="s">
+        <v>61</v>
+      </c>
+      <c r="I11" t="s">
+        <v>62</v>
+      </c>
+      <c r="J11" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="4">
@@ -792,7 +826,9 @@
       <c r="B12" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="2"/>
+      <c r="C12" s="2" t="s">
+        <v>4</v>
+      </c>
       <c r="D12" t="s">
         <v>37</v>
       </c>
@@ -810,7 +846,9 @@
       <c r="B13" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="2"/>
+      <c r="C13" s="2" t="s">
+        <v>4</v>
+      </c>
       <c r="D13" s="6" t="s">
         <v>41</v>
       </c>
@@ -837,7 +875,9 @@
       <c r="B14" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="2"/>
+      <c r="C14" s="2" t="s">
+        <v>4</v>
+      </c>
       <c r="D14" t="s">
         <v>46</v>
       </c>
@@ -1158,6 +1198,599 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75542B3A-A64F-4540-A2A5-DF5D1E8051F6}">
+  <dimension ref="A1:R49"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData>
+    <row r="1" spans="1:18">
+      <c r="A1" s="4"/>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" t="s">
+        <v>6</v>
+      </c>
+      <c r="O1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:18">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="P3" s="1"/>
+    </row>
+    <row r="4" spans="1:18">
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="P4" s="1"/>
+    </row>
+    <row r="5" spans="1:18">
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="P5" s="1"/>
+    </row>
+    <row r="6" spans="1:18">
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="P6" s="1"/>
+    </row>
+    <row r="7" spans="1:18">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="P7" s="1"/>
+    </row>
+    <row r="8" spans="1:18">
+      <c r="A8" s="4">
+        <v>1</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="P8" s="1"/>
+    </row>
+    <row r="9" spans="1:18">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="P9" s="1"/>
+    </row>
+    <row r="10" spans="1:18">
+      <c r="A10" s="4">
+        <v>3</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="P10" s="1"/>
+    </row>
+    <row r="11" spans="1:18">
+      <c r="A11" s="4">
+        <v>4</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="P11" s="1"/>
+    </row>
+    <row r="12" spans="1:18">
+      <c r="A12" s="4">
+        <v>5</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="P12" s="1"/>
+    </row>
+    <row r="13" spans="1:18">
+      <c r="A13" s="4">
+        <v>6</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="P13" s="1"/>
+    </row>
+    <row r="14" spans="1:18">
+      <c r="A14" s="4">
+        <v>1</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="P14" s="1"/>
+    </row>
+    <row r="15" spans="1:18">
+      <c r="A15" s="4">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="P15" s="1"/>
+    </row>
+    <row r="16" spans="1:18">
+      <c r="A16" s="4">
+        <v>3</v>
+      </c>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="P16" s="1"/>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17" s="4">
+        <v>4</v>
+      </c>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="P17" s="1"/>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18" s="4">
+        <v>5</v>
+      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="P18" s="1"/>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19" s="4">
+        <v>6</v>
+      </c>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="P19" s="1"/>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20" s="4">
+        <v>1</v>
+      </c>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="P20" s="1"/>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="P21" s="1"/>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="A22" s="4">
+        <v>3</v>
+      </c>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="P22" s="1"/>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23" s="4">
+        <v>4</v>
+      </c>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="P23" s="1"/>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="A24" s="4">
+        <v>5</v>
+      </c>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="P24" s="1"/>
+    </row>
+    <row r="25" spans="1:16">
+      <c r="A25" s="4">
+        <v>6</v>
+      </c>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="P25" s="1"/>
+    </row>
+    <row r="26" spans="1:16">
+      <c r="A26" s="4">
+        <v>1</v>
+      </c>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="P26" s="1"/>
+    </row>
+    <row r="27" spans="1:16">
+      <c r="A27" s="4">
+        <v>2</v>
+      </c>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="P27" s="1"/>
+    </row>
+    <row r="28" spans="1:16">
+      <c r="A28" s="4">
+        <v>3</v>
+      </c>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="P28" s="1"/>
+    </row>
+    <row r="29" spans="1:16">
+      <c r="A29" s="4">
+        <v>4</v>
+      </c>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="P29" s="1"/>
+    </row>
+    <row r="30" spans="1:16">
+      <c r="A30" s="4">
+        <v>5</v>
+      </c>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="P30" s="1"/>
+    </row>
+    <row r="31" spans="1:16">
+      <c r="A31" s="4">
+        <v>6</v>
+      </c>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="P31" s="1"/>
+    </row>
+    <row r="32" spans="1:16">
+      <c r="A32" s="4">
+        <v>1</v>
+      </c>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="P32" s="1"/>
+    </row>
+    <row r="33" spans="1:16">
+      <c r="A33" s="4">
+        <v>2</v>
+      </c>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="P33" s="1"/>
+    </row>
+    <row r="34" spans="1:16">
+      <c r="A34" s="4">
+        <v>3</v>
+      </c>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="P34" s="1"/>
+    </row>
+    <row r="35" spans="1:16">
+      <c r="A35" s="4">
+        <v>4</v>
+      </c>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="P35" s="1"/>
+    </row>
+    <row r="36" spans="1:16">
+      <c r="A36" s="4">
+        <v>5</v>
+      </c>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="M36" s="1"/>
+      <c r="P36" s="1"/>
+    </row>
+    <row r="37" spans="1:16">
+      <c r="A37" s="4">
+        <v>6</v>
+      </c>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="M37" s="1"/>
+      <c r="P37" s="1"/>
+    </row>
+    <row r="38" spans="1:16">
+      <c r="A38" s="4">
+        <v>1</v>
+      </c>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="J38" s="1"/>
+      <c r="M38" s="1"/>
+      <c r="P38" s="1"/>
+    </row>
+    <row r="39" spans="1:16">
+      <c r="A39" s="4">
+        <v>2</v>
+      </c>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="J39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="P39" s="1"/>
+    </row>
+    <row r="40" spans="1:16">
+      <c r="A40" s="4">
+        <v>3</v>
+      </c>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="J40" s="1"/>
+      <c r="M40" s="1"/>
+      <c r="P40" s="1"/>
+    </row>
+    <row r="41" spans="1:16">
+      <c r="A41" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16">
+      <c r="A42" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16">
+      <c r="A43" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16">
+      <c r="A44" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16">
+      <c r="A45" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16">
+      <c r="A46" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
+      <c r="A47" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16">
+      <c r="A48" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="4">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{CCC00043-25F2-486D-86A2-BF2EB23AFD34}">
+          <x14:formula1>
+            <xm:f>list!$A$1:$A$2</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:C40</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93CA1652-010D-4CD5-B2DA-C4FE25700D32}">
   <dimension ref="A1:F49"/>
   <sheetFormatPr defaultRowHeight="18"/>
@@ -1555,7 +2188,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A79A7F9-6C51-469C-A9B7-1B65800AEB29}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="18"/>
